--- a/Capstone_Documents/CogniCore_IT_Experts_ISO25010_N10.xlsx
+++ b/Capstone_Documents/CogniCore_IT_Experts_ISO25010_N10.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluators &amp; Raw Ratings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Numeric Matrix (SPSS Ready)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISO 25010 Summary Table" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -601,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -643,7 +642,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1547,185 +1545,8 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>MEAN</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Item / Subscale Means</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="17">
-        <f>AVERAGE(D5:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="17">
-        <f>AVERAGE(F5:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="17">
-        <f>AVERAGE(G5:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="17">
-        <f>AVERAGE(H5:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="17">
-        <f>AVERAGE(I5:I14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="17">
-        <f>AVERAGE(J5:J14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="17">
-        <f>AVERAGE(K5:K14)</f>
-        <v/>
-      </c>
-      <c r="L15" s="17">
-        <f>AVERAGE(L5:L14)</f>
-        <v/>
-      </c>
-      <c r="M15" s="17">
-        <f>AVERAGE(M5:M14)</f>
-        <v/>
-      </c>
-      <c r="N15" s="17">
-        <f>AVERAGE(N5:N14)</f>
-        <v/>
-      </c>
-      <c r="O15" s="17">
-        <f>AVERAGE(O5:O14)</f>
-        <v/>
-      </c>
-      <c r="P15" s="17">
-        <f>AVERAGE(P5:P14)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="17">
-        <f>AVERAGE(Q5:Q14)</f>
-        <v/>
-      </c>
-      <c r="R15" s="17">
-        <f>AVERAGE(R5:R14)</f>
-        <v/>
-      </c>
-      <c r="S15" s="17">
-        <f>AVERAGE(S5:S14)</f>
-        <v/>
-      </c>
-      <c r="T15" s="17">
-        <f>AVERAGE(T5:T14)</f>
-        <v/>
-      </c>
-      <c r="U15" s="18">
-        <f>AVERAGE(U5:U14)</f>
-        <v/>
-      </c>
-      <c r="V15" s="14">
-        <f>IF(U15&gt;=4.2,"Excellent",IF(U15&gt;=3.4,"Very Good",IF(U15&gt;=2.6,"Good",IF(U15&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-      <c r="W15" s="16" t="inlineStr">
-        <is>
-          <t>Overall Software Quality Mean</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>Standard Deviations (Sample SD)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr"/>
-      <c r="D16" s="22">
-        <f>STDEV.S(D5:D14)</f>
-        <v/>
-      </c>
-      <c r="E16" s="21" t="inlineStr"/>
-      <c r="F16" s="22">
-        <f>STDEV.S(F5:F14)</f>
-        <v/>
-      </c>
-      <c r="G16" s="22">
-        <f>STDEV.S(G5:G14)</f>
-        <v/>
-      </c>
-      <c r="H16" s="22">
-        <f>STDEV.S(H5:H14)</f>
-        <v/>
-      </c>
-      <c r="I16" s="22">
-        <f>STDEV.S(I5:I14)</f>
-        <v/>
-      </c>
-      <c r="J16" s="22">
-        <f>STDEV.S(J5:J14)</f>
-        <v/>
-      </c>
-      <c r="K16" s="22">
-        <f>STDEV.S(K5:K14)</f>
-        <v/>
-      </c>
-      <c r="L16" s="22">
-        <f>STDEV.S(L5:L14)</f>
-        <v/>
-      </c>
-      <c r="M16" s="22">
-        <f>STDEV.S(M5:M14)</f>
-        <v/>
-      </c>
-      <c r="N16" s="22">
-        <f>STDEV.S(N5:N14)</f>
-        <v/>
-      </c>
-      <c r="O16" s="22">
-        <f>STDEV.S(O5:O14)</f>
-        <v/>
-      </c>
-      <c r="P16" s="22">
-        <f>STDEV.S(P5:P14)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="22">
-        <f>STDEV.S(Q5:Q14)</f>
-        <v/>
-      </c>
-      <c r="R16" s="22">
-        <f>STDEV.S(R5:R14)</f>
-        <v/>
-      </c>
-      <c r="S16" s="22">
-        <f>STDEV.S(S5:S14)</f>
-        <v/>
-      </c>
-      <c r="T16" s="22">
-        <f>STDEV.S(T5:T14)</f>
-        <v/>
-      </c>
-      <c r="U16" s="23">
-        <f>STDEV.S(U5:U14)</f>
-        <v/>
-      </c>
-      <c r="V16" s="21" t="inlineStr"/>
-      <c r="W16" s="21" t="inlineStr">
-        <is>
-          <t>Evaluator-Level SD (N=10)</t>
-        </is>
-      </c>
-    </row>
+    <row r="15" ht="22" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:W2"/>
@@ -1741,7 +1562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1875,46 +1696,6 @@
           <t>Q15_Rel_TelemetryStore</t>
         </is>
       </c>
-      <c r="U1" s="24" t="inlineStr">
-        <is>
-          <t>Mean_FunctionalSuitability</t>
-        </is>
-      </c>
-      <c r="V1" s="24" t="inlineStr">
-        <is>
-          <t>Mean_SecurityMaintainability</t>
-        </is>
-      </c>
-      <c r="W1" s="24" t="inlineStr">
-        <is>
-          <t>Mean_Portability</t>
-        </is>
-      </c>
-      <c r="X1" s="24" t="inlineStr">
-        <is>
-          <t>Mean_PerformanceEfficiency</t>
-        </is>
-      </c>
-      <c r="Y1" s="24" t="inlineStr">
-        <is>
-          <t>Mean_Compatibility</t>
-        </is>
-      </c>
-      <c r="Z1" s="24" t="inlineStr">
-        <is>
-          <t>Mean_Usability</t>
-        </is>
-      </c>
-      <c r="AA1" s="24" t="inlineStr">
-        <is>
-          <t>Mean_Reliability</t>
-        </is>
-      </c>
-      <c r="AB1" s="24" t="inlineStr">
-        <is>
-          <t>Overall_Mean</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -1985,38 +1766,6 @@
       <c r="T2" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="U2" s="25">
-        <f>AVERAGE(F2:H2)</f>
-        <v/>
-      </c>
-      <c r="V2" s="25">
-        <f>AVERAGE(I2:K2)</f>
-        <v/>
-      </c>
-      <c r="W2" s="25">
-        <f>L2</f>
-        <v/>
-      </c>
-      <c r="X2" s="25">
-        <f>AVERAGE(M2:N2)</f>
-        <v/>
-      </c>
-      <c r="Y2" s="25">
-        <f>AVERAGE(O2:P2)</f>
-        <v/>
-      </c>
-      <c r="Z2" s="25">
-        <f>IF(COUNT(Q2:R2)&gt;0, AVERAGE(Q2:R2), "")</f>
-        <v/>
-      </c>
-      <c r="AA2" s="25">
-        <f>AVERAGE(S2:T2)</f>
-        <v/>
-      </c>
-      <c r="AB2" s="7">
-        <f>AVERAGE(F2:T2)</f>
-        <v/>
-      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -2083,38 +1832,6 @@
       <c r="T3" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="U3" s="26">
-        <f>AVERAGE(F3:H3)</f>
-        <v/>
-      </c>
-      <c r="V3" s="26">
-        <f>AVERAGE(I3:K3)</f>
-        <v/>
-      </c>
-      <c r="W3" s="26">
-        <f>L3</f>
-        <v/>
-      </c>
-      <c r="X3" s="26">
-        <f>AVERAGE(M3:N3)</f>
-        <v/>
-      </c>
-      <c r="Y3" s="26">
-        <f>AVERAGE(O3:P3)</f>
-        <v/>
-      </c>
-      <c r="Z3" s="26">
-        <f>IF(COUNT(Q3:R3)&gt;0, AVERAGE(Q3:R3), "")</f>
-        <v/>
-      </c>
-      <c r="AA3" s="26">
-        <f>AVERAGE(S3:T3)</f>
-        <v/>
-      </c>
-      <c r="AB3" s="12">
-        <f>AVERAGE(F3:T3)</f>
-        <v/>
-      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -2185,38 +1902,6 @@
       <c r="T4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="U4" s="25">
-        <f>AVERAGE(F4:H4)</f>
-        <v/>
-      </c>
-      <c r="V4" s="25">
-        <f>AVERAGE(I4:K4)</f>
-        <v/>
-      </c>
-      <c r="W4" s="25">
-        <f>L4</f>
-        <v/>
-      </c>
-      <c r="X4" s="25">
-        <f>AVERAGE(M4:N4)</f>
-        <v/>
-      </c>
-      <c r="Y4" s="25">
-        <f>AVERAGE(O4:P4)</f>
-        <v/>
-      </c>
-      <c r="Z4" s="25">
-        <f>IF(COUNT(Q4:R4)&gt;0, AVERAGE(Q4:R4), "")</f>
-        <v/>
-      </c>
-      <c r="AA4" s="25">
-        <f>AVERAGE(S4:T4)</f>
-        <v/>
-      </c>
-      <c r="AB4" s="7">
-        <f>AVERAGE(F4:T4)</f>
-        <v/>
-      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -2287,38 +1972,6 @@
       <c r="T5" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="U5" s="26">
-        <f>AVERAGE(F5:H5)</f>
-        <v/>
-      </c>
-      <c r="V5" s="26">
-        <f>AVERAGE(I5:K5)</f>
-        <v/>
-      </c>
-      <c r="W5" s="26">
-        <f>L5</f>
-        <v/>
-      </c>
-      <c r="X5" s="26">
-        <f>AVERAGE(M5:N5)</f>
-        <v/>
-      </c>
-      <c r="Y5" s="26">
-        <f>AVERAGE(O5:P5)</f>
-        <v/>
-      </c>
-      <c r="Z5" s="26">
-        <f>IF(COUNT(Q5:R5)&gt;0, AVERAGE(Q5:R5), "")</f>
-        <v/>
-      </c>
-      <c r="AA5" s="26">
-        <f>AVERAGE(S5:T5)</f>
-        <v/>
-      </c>
-      <c r="AB5" s="12">
-        <f>AVERAGE(F5:T5)</f>
-        <v/>
-      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -2389,38 +2042,6 @@
       <c r="T6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="U6" s="25">
-        <f>AVERAGE(F6:H6)</f>
-        <v/>
-      </c>
-      <c r="V6" s="25">
-        <f>AVERAGE(I6:K6)</f>
-        <v/>
-      </c>
-      <c r="W6" s="25">
-        <f>L6</f>
-        <v/>
-      </c>
-      <c r="X6" s="25">
-        <f>AVERAGE(M6:N6)</f>
-        <v/>
-      </c>
-      <c r="Y6" s="25">
-        <f>AVERAGE(O6:P6)</f>
-        <v/>
-      </c>
-      <c r="Z6" s="25">
-        <f>IF(COUNT(Q6:R6)&gt;0, AVERAGE(Q6:R6), "")</f>
-        <v/>
-      </c>
-      <c r="AA6" s="25">
-        <f>AVERAGE(S6:T6)</f>
-        <v/>
-      </c>
-      <c r="AB6" s="7">
-        <f>AVERAGE(F6:T6)</f>
-        <v/>
-      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -2487,38 +2108,6 @@
       <c r="T7" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="U7" s="26">
-        <f>AVERAGE(F7:H7)</f>
-        <v/>
-      </c>
-      <c r="V7" s="26">
-        <f>AVERAGE(I7:K7)</f>
-        <v/>
-      </c>
-      <c r="W7" s="26">
-        <f>L7</f>
-        <v/>
-      </c>
-      <c r="X7" s="26">
-        <f>AVERAGE(M7:N7)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="26">
-        <f>AVERAGE(O7:P7)</f>
-        <v/>
-      </c>
-      <c r="Z7" s="26">
-        <f>IF(COUNT(Q7:R7)&gt;0, AVERAGE(Q7:R7), "")</f>
-        <v/>
-      </c>
-      <c r="AA7" s="26">
-        <f>AVERAGE(S7:T7)</f>
-        <v/>
-      </c>
-      <c r="AB7" s="12">
-        <f>AVERAGE(F7:T7)</f>
-        <v/>
-      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -2589,38 +2178,6 @@
       <c r="T8" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="U8" s="25">
-        <f>AVERAGE(F8:H8)</f>
-        <v/>
-      </c>
-      <c r="V8" s="25">
-        <f>AVERAGE(I8:K8)</f>
-        <v/>
-      </c>
-      <c r="W8" s="25">
-        <f>L8</f>
-        <v/>
-      </c>
-      <c r="X8" s="25">
-        <f>AVERAGE(M8:N8)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="25">
-        <f>AVERAGE(O8:P8)</f>
-        <v/>
-      </c>
-      <c r="Z8" s="25">
-        <f>IF(COUNT(Q8:R8)&gt;0, AVERAGE(Q8:R8), "")</f>
-        <v/>
-      </c>
-      <c r="AA8" s="25">
-        <f>AVERAGE(S8:T8)</f>
-        <v/>
-      </c>
-      <c r="AB8" s="7">
-        <f>AVERAGE(F8:T8)</f>
-        <v/>
-      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -2691,38 +2248,6 @@
       <c r="T9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="U9" s="26">
-        <f>AVERAGE(F9:H9)</f>
-        <v/>
-      </c>
-      <c r="V9" s="26">
-        <f>AVERAGE(I9:K9)</f>
-        <v/>
-      </c>
-      <c r="W9" s="26">
-        <f>L9</f>
-        <v/>
-      </c>
-      <c r="X9" s="26">
-        <f>AVERAGE(M9:N9)</f>
-        <v/>
-      </c>
-      <c r="Y9" s="26">
-        <f>AVERAGE(O9:P9)</f>
-        <v/>
-      </c>
-      <c r="Z9" s="26">
-        <f>IF(COUNT(Q9:R9)&gt;0, AVERAGE(Q9:R9), "")</f>
-        <v/>
-      </c>
-      <c r="AA9" s="26">
-        <f>AVERAGE(S9:T9)</f>
-        <v/>
-      </c>
-      <c r="AB9" s="12">
-        <f>AVERAGE(F9:T9)</f>
-        <v/>
-      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -2793,38 +2318,6 @@
       <c r="T10" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="U10" s="25">
-        <f>AVERAGE(F10:H10)</f>
-        <v/>
-      </c>
-      <c r="V10" s="25">
-        <f>AVERAGE(I10:K10)</f>
-        <v/>
-      </c>
-      <c r="W10" s="25">
-        <f>L10</f>
-        <v/>
-      </c>
-      <c r="X10" s="25">
-        <f>AVERAGE(M10:N10)</f>
-        <v/>
-      </c>
-      <c r="Y10" s="25">
-        <f>AVERAGE(O10:P10)</f>
-        <v/>
-      </c>
-      <c r="Z10" s="25">
-        <f>IF(COUNT(Q10:R10)&gt;0, AVERAGE(Q10:R10), "")</f>
-        <v/>
-      </c>
-      <c r="AA10" s="25">
-        <f>AVERAGE(S10:T10)</f>
-        <v/>
-      </c>
-      <c r="AB10" s="7">
-        <f>AVERAGE(F10:T10)</f>
-        <v/>
-      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
@@ -2894,993 +2387,9 @@
       </c>
       <c r="T11" s="11" t="n">
         <v>4</v>
-      </c>
-      <c r="U11" s="26">
-        <f>AVERAGE(F11:H11)</f>
-        <v/>
-      </c>
-      <c r="V11" s="26">
-        <f>AVERAGE(I11:K11)</f>
-        <v/>
-      </c>
-      <c r="W11" s="26">
-        <f>L11</f>
-        <v/>
-      </c>
-      <c r="X11" s="26">
-        <f>AVERAGE(M11:N11)</f>
-        <v/>
-      </c>
-      <c r="Y11" s="26">
-        <f>AVERAGE(O11:P11)</f>
-        <v/>
-      </c>
-      <c r="Z11" s="26">
-        <f>IF(COUNT(Q11:R11)&gt;0, AVERAGE(Q11:R11), "")</f>
-        <v/>
-      </c>
-      <c r="AA11" s="26">
-        <f>AVERAGE(S11:T11)</f>
-        <v/>
-      </c>
-      <c r="AB11" s="12">
-        <f>AVERAGE(F11:T11)</f>
-        <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>COGNICORE: ISO/IEC 25010 SOFTWARE QUALITY EVALUATION SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Academic Summary Table (N=10 Evaluators, 7 Quality Dimensions, 15 Items, UPHSD Likert Standard)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Category / Characteristic</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Item ID</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Quality Indicator / Questionnaire Statement</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Std. Dev</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Verbal Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="21" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Functional Suitability</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>The system's Dynamic Difficulty Adjustment (DDA) logic correctly scales based on real-time user input.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!F15</f>
-        <v/>
-      </c>
-      <c r="F5" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!F16</f>
-        <v/>
-      </c>
-      <c r="G5" s="4">
-        <f>IF(E5&gt;=4.2,"Excellent",IF(E5&gt;=3.4,"Very Good",IF(E5&gt;=2.6,"Good",IF(E5&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Functional Suitability</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>The Random Forest Classifier accurately processes data to categorize users into the correct Cognitive Archetypes.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!G15</f>
-        <v/>
-      </c>
-      <c r="F6" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!G16</f>
-        <v/>
-      </c>
-      <c r="G6" s="4">
-        <f>IF(E6&gt;=4.2,"Excellent",IF(E6&gt;=3.4,"Very Good",IF(E6&gt;=2.6,"Good",IF(E6&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="21" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Functional Suitability</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>The system fulfills all specified programmatic objectives to provide accurate reports on student cognitive skills and analysis across the 4 domains.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!H15</f>
-        <v/>
-      </c>
-      <c r="F7" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!H16</f>
-        <v/>
-      </c>
-      <c r="G7" s="4">
-        <f>IF(E7&gt;=4.2,"Excellent",IF(E7&gt;=3.4,"Very Good",IF(E7&gt;=2.6,"Good",IF(E7&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="21" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Functional Suitability (Subscale Composite)</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr"/>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>Subscale Composite Score (3 Items, N=10 Evaluators)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="23">
-        <f>AVERAGE('Numeric Matrix (SPSS Ready)'!U2:U11)</f>
-        <v/>
-      </c>
-      <c r="F8" s="23">
-        <f>STDEV.S('Numeric Matrix (SPSS Ready)'!U2:U11)</f>
-        <v/>
-      </c>
-      <c r="G8" s="19">
-        <f>IF(E8&gt;=4.2,"Excellent",IF(E8&gt;=3.4,"Very Good",IF(E8&gt;=2.6,"Good",IF(E8&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Security &amp; Maintainability</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>User login credentials and profile data are properly secured and encrypted within the database.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!I15</f>
-        <v/>
-      </c>
-      <c r="F9" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!I16</f>
-        <v/>
-      </c>
-      <c r="G9" s="4">
-        <f>IF(E9&gt;=4.2,"Excellent",IF(E9&gt;=3.4,"Very Good",IF(E9&gt;=2.6,"Good",IF(E9&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Security &amp; Maintainability</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>The source code is logically structured, commented, and modular, making the system easy to update.</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!J15</f>
-        <v/>
-      </c>
-      <c r="F10" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!J16</f>
-        <v/>
-      </c>
-      <c r="G10" s="4">
-        <f>IF(E10&gt;=4.2,"Excellent",IF(E10&gt;=3.4,"Very Good",IF(E10&gt;=2.6,"Good",IF(E10&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Security &amp; Maintainability</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Additional cognitive game modules could be integrated into the framework without breaking the existing codebase.</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!K15</f>
-        <v/>
-      </c>
-      <c r="F11" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!K16</f>
-        <v/>
-      </c>
-      <c r="G11" s="4">
-        <f>IF(E11&gt;=4.2,"Excellent",IF(E11&gt;=3.4,"Very Good",IF(E11&gt;=2.6,"Good",IF(E11&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="21" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Security &amp; Maintainability (Subscale Composite)</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>Subscale Composite Score (3 Items, N=10 Evaluators)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="23">
-        <f>AVERAGE('Numeric Matrix (SPSS Ready)'!V2:V11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="23">
-        <f>STDEV.S('Numeric Matrix (SPSS Ready)'!V2:V11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="19">
-        <f>IF(E12&gt;=4.2,"Excellent",IF(E12&gt;=3.4,"Very Good",IF(E12&gt;=2.6,"Good",IF(E12&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Portability</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>The system can be easily deployed and run on different local environments or public hosting servers.</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!L15</f>
-        <v/>
-      </c>
-      <c r="F13" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!L16</f>
-        <v/>
-      </c>
-      <c r="G13" s="4">
-        <f>IF(E13&gt;=4.2,"Excellent",IF(E13&gt;=3.4,"Very Good",IF(E13&gt;=2.6,"Good",IF(E13&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>Portability (Subscale Composite)</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>Subscale Composite Score (1 Item, N=10 Evaluators)</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="23">
-        <f>AVERAGE('Numeric Matrix (SPSS Ready)'!W2:W11)</f>
-        <v/>
-      </c>
-      <c r="F14" s="23">
-        <f>STDEV.S('Numeric Matrix (SPSS Ready)'!W2:W11)</f>
-        <v/>
-      </c>
-      <c r="G14" s="19">
-        <f>IF(E14&gt;=4.2,"Excellent",IF(E14&gt;=3.4,"Very Good",IF(E14&gt;=2.6,"Good",IF(E14&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Performance Efficiency</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>The Phaser.io mini-games load and respond quickly without hardware-induced latency.</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!M15</f>
-        <v/>
-      </c>
-      <c r="F15" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!M16</f>
-        <v/>
-      </c>
-      <c r="G15" s="4">
-        <f>IF(E15&gt;=4.2,"Excellent",IF(E15&gt;=3.4,"Very Good",IF(E15&gt;=2.6,"Good",IF(E15&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Performance Efficiency</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>The Python/Flask backend processes the AI evaluation route efficiently under load.</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!N15</f>
-        <v/>
-      </c>
-      <c r="F16" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!N16</f>
-        <v/>
-      </c>
-      <c r="G16" s="4">
-        <f>IF(E16&gt;=4.2,"Excellent",IF(E16&gt;=3.4,"Very Good",IF(E16&gt;=2.6,"Good",IF(E16&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="21" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>Performance Efficiency (Subscale Composite)</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr"/>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>Subscale Composite Score (2 Items, N=10 Evaluators)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" s="23">
-        <f>AVERAGE('Numeric Matrix (SPSS Ready)'!X2:X11)</f>
-        <v/>
-      </c>
-      <c r="F17" s="23">
-        <f>STDEV.S('Numeric Matrix (SPSS Ready)'!X2:X11)</f>
-        <v/>
-      </c>
-      <c r="G17" s="19">
-        <f>IF(E17&gt;=4.2,"Excellent",IF(E17&gt;=3.4,"Very Good",IF(E17&gt;=2.6,"Good",IF(E17&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="21" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Compatibility</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>The web application functions correctly across different modern web browsers (Chrome, Edge, Firefox).</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!O15</f>
-        <v/>
-      </c>
-      <c r="F18" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!O16</f>
-        <v/>
-      </c>
-      <c r="G18" s="4">
-        <f>IF(E18&gt;=4.2,"Excellent",IF(E18&gt;=3.4,"Very Good",IF(E18&gt;=2.6,"Good",IF(E18&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Compatibility</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>The React.js frontend integrates seamlessly with the Python backend API.</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!P15</f>
-        <v/>
-      </c>
-      <c r="F19" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!P16</f>
-        <v/>
-      </c>
-      <c r="G19" s="4">
-        <f>IF(E19&gt;=4.2,"Excellent",IF(E19&gt;=3.4,"Very Good",IF(E19&gt;=2.6,"Good",IF(E19&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>Compatibility (Subscale Composite)</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>Subscale Composite Score (2 Items, N=10 Evaluators)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" s="23">
-        <f>AVERAGE('Numeric Matrix (SPSS Ready)'!Y2:Y11)</f>
-        <v/>
-      </c>
-      <c r="F20" s="23">
-        <f>STDEV.S('Numeric Matrix (SPSS Ready)'!Y2:Y11)</f>
-        <v/>
-      </c>
-      <c r="G20" s="19">
-        <f>IF(E20&gt;=4.2,"Excellent",IF(E20&gt;=3.4,"Very Good",IF(E20&gt;=2.6,"Good",IF(E20&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Usability</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>The AI Analytics Dashboard code accurately renders the visualization of data (e.g., Radar Charts).</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!Q15</f>
-        <v/>
-      </c>
-      <c r="F21" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!Q16</f>
-        <v/>
-      </c>
-      <c r="G21" s="4">
-        <f>IF(E21&gt;=4.2,"Excellent",IF(E21&gt;=3.4,"Very Good",IF(E21&gt;=2.6,"Good",IF(E21&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Usability</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>The administrative and system navigation flows are logically organized.</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!R15</f>
-        <v/>
-      </c>
-      <c r="F22" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!R16</f>
-        <v/>
-      </c>
-      <c r="G22" s="4">
-        <f>IF(E22&gt;=4.2,"Excellent",IF(E22&gt;=3.4,"Very Good",IF(E22&gt;=2.6,"Good",IF(E22&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="21" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Usability (Subscale Composite)</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr"/>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>Subscale Composite Score (2 Items, N=8 Valid Evaluators)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" s="23">
-        <f>AVERAGE('Numeric Matrix (SPSS Ready)'!Z2:Z11)</f>
-        <v/>
-      </c>
-      <c r="F23" s="23">
-        <f>STDEV.S('Numeric Matrix (SPSS Ready)'!Z2:Z11)</f>
-        <v/>
-      </c>
-      <c r="G23" s="19">
-        <f>IF(E23&gt;=4.2,"Excellent",IF(E23&gt;=3.4,"Very Good",IF(E23&gt;=2.6,"Good",IF(E23&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>The system recovers smoothly in the event of an input error, spam-clicking, or interrupted gameplay.</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!S15</f>
-        <v/>
-      </c>
-      <c r="F24" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!S16</f>
-        <v/>
-      </c>
-      <c r="G24" s="4">
-        <f>IF(E24&gt;=4.2,"Excellent",IF(E24&gt;=3.4,"Very Good",IF(E24&gt;=2.6,"Good",IF(E24&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>The game tracks and stores gameplay telemetry consistently without data loss.</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!T15</f>
-        <v/>
-      </c>
-      <c r="F25" s="25">
-        <f>'Evaluators &amp; Raw Ratings'!T16</f>
-        <v/>
-      </c>
-      <c r="G25" s="4">
-        <f>IF(E25&gt;=4.2,"Excellent",IF(E25&gt;=3.4,"Very Good",IF(E25&gt;=2.6,"Good",IF(E25&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="21" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>Reliability (Subscale Composite)</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr"/>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>Subscale Composite Score (2 Items, N=10 Evaluators)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" s="23">
-        <f>AVERAGE('Numeric Matrix (SPSS Ready)'!AA2:AA11)</f>
-        <v/>
-      </c>
-      <c r="F26" s="23">
-        <f>STDEV.S('Numeric Matrix (SPSS Ready)'!AA2:AA11)</f>
-        <v/>
-      </c>
-      <c r="G26" s="19">
-        <f>IF(E26&gt;=4.2,"Excellent",IF(E26&gt;=3.4,"Very Good",IF(E26&gt;=2.6,"Good",IF(E26&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="27" t="inlineStr">
-        <is>
-          <t>OVERALL ISO/IEC 25010 QUALITY</t>
-        </is>
-      </c>
-      <c r="B27" s="28" t="inlineStr"/>
-      <c r="C27" s="27" t="inlineStr">
-        <is>
-          <t>Overall System Quality (Evaluator Composite Mean, N=10 Evaluators)</t>
-        </is>
-      </c>
-      <c r="D27" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" s="29">
-        <f>AVERAGE('Numeric Matrix (SPSS Ready)'!AB2:AB11)</f>
-        <v/>
-      </c>
-      <c r="F27" s="29">
-        <f>STDEV.S('Numeric Matrix (SPSS Ready)'!AB2:AB11)</f>
-        <v/>
-      </c>
-      <c r="G27" s="28">
-        <f>IF(E27&gt;=4.2,"Excellent",IF(E27&gt;=3.4,"Very Good",IF(E27&gt;=2.6,"Good",IF(E27&gt;=1.8,"Fair","Poor"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>Likert Scale Reference (UPHSD Academic Standard):</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="30" t="inlineStr">
-        <is>
-          <t>4.20 - 5.00</t>
-        </is>
-      </c>
-      <c r="B30" s="30" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-      <c r="C30" s="31" t="inlineStr">
-        <is>
-          <t>System demonstrates optimal software engineering standard / Strongly Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="30" t="inlineStr">
-        <is>
-          <t>3.40 - 4.19</t>
-        </is>
-      </c>
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>Very Good</t>
-        </is>
-      </c>
-      <c r="C31" s="31" t="inlineStr">
-        <is>
-          <t>System meets standard specifications with minor optional enhancements / Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>2.60 - 3.39</t>
-        </is>
-      </c>
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="C32" s="31" t="inlineStr">
-        <is>
-          <t>Acceptable performance with moderate revision needed / Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>1.80 - 2.59</t>
-        </is>
-      </c>
-      <c r="B33" s="30" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-      <c r="C33" s="31" t="inlineStr">
-        <is>
-          <t>Substantial performance limitations / Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="30" t="inlineStr">
-        <is>
-          <t>1.00 - 1.79</t>
-        </is>
-      </c>
-      <c r="B34" s="30" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="C34" s="31" t="inlineStr">
-        <is>
-          <t>Major defect or non-functional characteristic / Strongly Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="30" t="inlineStr">
-        <is>
-          <t>Psychometric Reliability &amp; Statistician Notes:</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t>Cronbach's Alpha (k=15 items)</t>
-        </is>
-      </c>
-      <c r="B37" s="30" t="inlineStr">
-        <is>
-          <t>0.9329</t>
-        </is>
-      </c>
-      <c r="C37" s="31" t="inlineStr">
-        <is>
-          <t>Excellent internal consistency across completed instrument cases (N=8).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="30" t="inlineStr">
-        <is>
-          <t>Cronbach's Alpha (k=13 common items)</t>
-        </is>
-      </c>
-      <c r="B38" s="30" t="inlineStr">
-        <is>
-          <t>0.9102</t>
-        </is>
-      </c>
-      <c r="C38" s="31" t="inlineStr">
-        <is>
-          <t>Excellent internal consistency across all N=10 evaluators.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="30" t="inlineStr">
-        <is>
-          <t>Handling of Missing Values</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="inlineStr">
-        <is>
-          <t>Listwise / Pairwise</t>
-        </is>
-      </c>
-      <c r="C39" s="31" t="inlineStr">
-        <is>
-          <t>EXP-02 &amp; EXP-06 omitted Q12 &amp; Q13; preserved as empty/null to avoid artificial imputation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="30" t="inlineStr">
-        <is>
-          <t>Unit of Analysis (Subscale SDs)</t>
-        </is>
-      </c>
-      <c r="B40" s="30" t="inlineStr">
-        <is>
-          <t>Evaluator Level</t>
-        </is>
-      </c>
-      <c r="C40" s="31" t="inlineStr">
-        <is>
-          <t>Reported Subscale SD reflects variance between evaluators (df=9) rather than item pooling.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>